--- a/daily_matches/job_matches_2026-07-09.xlsx
+++ b/daily_matches/job_matches_2026-07-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Applied AI Solutions Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MasterControl</t>
+          <t>Allocate</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Redshift, Docker, Kubernetes, Git, Redshift</t>
+          <t>LangChain, RAG, LLaMA, Pinecone, S3, EC2, Glue, Athena, Redshift, Data Lake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118d0099ca655fbf</t>
+          <t>https://www.indeed.com/viewjob?jk=53d67e2c6a917d94</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevOps Engineering Intern</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3c1a2d78dbef72</t>
+          <t>https://www.indeed.com/viewjob?jk=05d26e9d276de69c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SynergenX Health Holdings</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, MLflow, CI/CD, Git, Databricks, PySpark, Power BI, Python</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae3f933ced0782ac</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e03f61f231e6f7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Software Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0058648e8ec47e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc3d7f6b293b8798</t>
         </is>
       </c>
     </row>
@@ -613,20 +613,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c645cbff1d3870</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c60c8af1cd2657</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Machine Learning Engineer - Marketing and Corporate Systems (ML Ops)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, GCP Vertex AI, Azure ML, FastAPI, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24d0af560e9bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=030402bec7177519</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Primerica</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
+          <t>Copilot, S3, EC2, Kinesis, Kubernetes, Terraform, Git, Databricks, Kafka, Tableau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9885cdd8f6f0e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=f05d2b3593772f33</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Cortex, Athena, Data Lake, Apache Airflow, Git, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98424ae5c6548f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=e7544b63dae902ba</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Visualization Professional</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Brook INC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Redshift, Git, Snowflake, Redshift, Power BI, SQL, R</t>
+          <t>Data Scientist, RAG, Copilot, BigQuery, Kinesis, Terraform, Git, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5cb0f896558c2be</t>
+          <t>https://www.indeed.com/viewjob?jk=d754b9ca64323d6e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Implementation Solutions Architect</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>New Relic</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, S3, EC2, Athena, Redshift, CI/CD, Git, Redshift, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70cdcaee06adcf4</t>
+          <t>https://www.indeed.com/viewjob?jk=33d347250384414c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer II – AI Engineer (w/ skills in Deployment)</t>
+          <t>AI Full Stack Developer / Architect (ON-SITE ONLY)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e55e870f928ed4f7</t>
+          <t>https://www.indeed.com/viewjob?jk=10066f0332c5b380</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Research Programmer II</t>
+          <t>Senior Engineer, Back-End</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35a7385698d126a</t>
+          <t>https://www.indeed.com/viewjob?jk=bb18c698bf09905f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>eCommerce Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Gemini, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2df7a628e2437ab</t>
+          <t>https://www.indeed.com/viewjob?jk=6d74b5348b7fd931</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Redshift, Synapse, Snowflake, Redshift, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c9ae05aae3a3346</t>
+          <t>https://www.indeed.com/viewjob?jk=139ae06dd742f9ff</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, MLflow, Kubernetes, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2bd9398f26eef1f</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd476055d1792da</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, MLflow, Kubernetes, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24ab3dd1c44b7d40</t>
+          <t>https://www.indeed.com/viewjob?jk=31499f71cdecb8b3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, MLflow, Kubernetes, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbcdb0aa48ed330c</t>
+          <t>https://www.indeed.com/viewjob?jk=929da1d9b8d02da7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, MLflow, Kubernetes, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5db46787bc727540</t>
+          <t>https://www.indeed.com/viewjob?jk=990f003e318fc7ee</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, MLflow, Kubernetes, Git, Databricks, Python, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7458d01959506806</t>
+          <t>https://www.indeed.com/viewjob?jk=799fa0365ab63c88</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Git, Databricks, MongoDB, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=187a662f10a97202</t>
+          <t>https://www.indeed.com/viewjob?jk=e65e864080e6f228</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Git, Databricks, MongoDB, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43eda394c8d0f10</t>
+          <t>https://www.indeed.com/viewjob?jk=379a672460ecff73</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Data Scientist - National Federal Tax Services</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc9f4af96338d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=c837980bd637052e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>The Voleon Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Athena, BigQuery, Docker, Kubernetes, Snowflake, BigQuery, Python, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0afca03dbb6d3c2</t>
+          <t>https://www.indeed.com/viewjob?jk=db0d7f2f67ae2037</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>The Voleon Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Athena, BigQuery, Docker, Kubernetes, Snowflake, BigQuery, Python, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0328e58d84dacf2</t>
+          <t>https://www.indeed.com/viewjob?jk=fc5c1209d3bf9f82</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>The Voleon Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Athena, BigQuery, Docker, Kubernetes, Snowflake, BigQuery, Python, R, Java</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6191c51f06d35aac</t>
+          <t>https://www.indeed.com/viewjob?jk=288370e41eee0f1c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Data Insights &amp; Analytics Senior Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>AlixPartners</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Data Lake, CI/CD, Snowflake, Databricks, PySpark, Power BI, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ea6fd5377655efc</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3a4117d82354a9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>ProCare solutions</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, MongoDB, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=973470b36004bc28</t>
+          <t>https://www.indeed.com/viewjob?jk=59621637da2df488</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7840a3133c0b778</t>
+          <t>https://www.indeed.com/viewjob?jk=e3d31f0c32f7c708</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85aff0cf1a924c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=839dff8154a525fe</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Software Engineer in Test – Performance Testing (Remote - US)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Nextech Systems</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54002f2b49daf139</t>
+          <t>https://www.indeed.com/viewjob?jk=ece1679bb1b68d39</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e421a09e76cb3baa</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c144c9967d41f3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior AI Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>BillGO, Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, S3, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b323b4d3f012056c</t>
+          <t>https://www.indeed.com/viewjob?jk=35205d14927a9d7c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Machine Learning Engineer I</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Gen Digital Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>Machine Learning Engineer, RAG, BigQuery, Git, BigQuery, Python, SQL, R, A/B Testing</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b389a8e70f1eda6f</t>
+          <t>https://www.indeed.com/viewjob?jk=e8378c32413f340a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, CI/CD, Git, NoSQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b613118383189b7</t>
+          <t>https://www.indeed.com/viewjob?jk=146fecf9cd2b1c5d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior Security Research Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Exabeam</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fcad206c910b60</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2887f3d4d109e5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Artificial Intelligence Engineer I</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Baylor College of Medicine</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ef447cbdac1e97</t>
+          <t>https://www.indeed.com/viewjob?jk=8822e9a8bbb9ce82</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Associate Software Engineer – Full Stack (AI First)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, Copilot, CI/CD, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,137 +1756,137 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6418ebd1d1d2d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=16b99e4398857e63</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ea0a966699cc46</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc96cc8b1713d38</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior Site Reliability Engineer, Observability</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Ripple</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>RAG, CI/CD, Terraform, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a52236c7d3098d2</t>
+          <t>https://www.indeed.com/viewjob?jk=4aab1e166ca443aa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior Site Reliability Engineer, Observability</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Ripple</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>RAG, CI/CD, Terraform, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc07cad3615a0ee</t>
+          <t>https://www.indeed.com/viewjob?jk=c3820ff49875cde5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Sr. 3D C++ Software Engineer (On-site)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Envista Holdings</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Pomona, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, Git, Python, R, C++, Scala, Optimization</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,637 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d5789ee04c3d3e</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=728ea89db1cf0cac</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b35dbd9a8bec5e74</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=519baefa33119517</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e007c4793c531f31</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b99c5b37a47abe54</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bddd8d911ac9ff72</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e85dea0c266c05ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Data Engineer - TEM, Python, Julia</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, Git, Snowflake, Databricks, Python, SQL, R, Julia, Scala</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b970d806f3fd5637</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Python/PySpark/AWS</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, CI/CD, Snowflake, Databricks, PySpark, Hadoop, Python, R</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=886d622b68bd75e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>AI DevOps. Engineer</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Expedient</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3d1834f43ee8441</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Data Engineer - Oracle data integrato and BI</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>RAG, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea82fd770b87f655</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>LTM Limited</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, MongoDB, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f31e83496e01df6</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Network Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Ghost</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, CI/CD, GitHub Actions, Terraform, Git, R, Scala</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99d4fb0f1662b464</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Cloud Platform</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Guidewire</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15fd6ac81cf3ec73</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Swinerton</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Concord, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AI Engineer, Machine Learning Engineer, LangChain, LLaMA, Copilot, CI/CD, Databricks, R, Scala</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=882ad5d830fa5061</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Software Engineer II – AI Engineer (w/ skills in AI Data Privacy, Security &amp; Governance Specialty)</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Robert Half</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>San Ramon, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, CI/CD, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b53ab2d62cda446</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Turtle Rock Studios</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Snowflake, Redshift, Python, SQL, R, Java, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe8e31f224a7988</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>DevSecOps Engineer</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>BD</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Sparks, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb883bea294c496d</t>
+          <t>https://www.indeed.com/viewjob?jk=089b12b1ad077cc1</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-09.xlsx
+++ b/daily_matches/job_matches_2026-07-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,192 +468,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer-Tech Ex AI Assets Foundry Team</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Allocate</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Pinecone, S3, EC2, Glue, Athena, Redshift, Data Lake</t>
+          <t>Generative AI, RAG, Prompt Engineering, S3, Docker, CI/CD, Terraform, Git, Databricks, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d67e2c6a917d94</t>
+          <t>https://www.indeed.com/viewjob?jk=0b83db5488d77940</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer- Tech Ex AI Assets Foundry Team</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark</t>
+          <t>Generative AI, RAG, Prompt Engineering, S3, Docker, CI/CD, Terraform, Git, Databricks, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d26e9d276de69c</t>
+          <t>https://www.indeed.com/viewjob?jk=843e1428f95c6703</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e03f61f231e6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=2597cb0394454250</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc3d7f6b293b8798</t>
+          <t>https://www.indeed.com/viewjob?jk=5750fd5dfd3a42b6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c60c8af1cd2657</t>
+          <t>https://www.indeed.com/viewjob?jk=92ba3bedf63fbf59</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer - Marketing and Corporate Systems (ML Ops)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, GCP Vertex AI, Azure ML, FastAPI, CI/CD</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=030402bec7177519</t>
+          <t>https://www.indeed.com/viewjob?jk=1edfd13da48a51da</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Primerica</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Copilot, S3, EC2, Kinesis, Kubernetes, Terraform, Git, Databricks, Kafka, Tableau</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f05d2b3593772f33</t>
+          <t>https://www.indeed.com/viewjob?jk=59d384bdaf8bd855</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,112 +731,112 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Cortex, Athena, Data Lake, Apache Airflow, Git, Snowflake</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7544b63dae902ba</t>
+          <t>https://www.indeed.com/viewjob?jk=408f964c06b99ef3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Brook INC</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, BigQuery, Kinesis, Terraform, Git, Snowflake, Databricks, BigQuery</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d754b9ca64323d6e</t>
+          <t>https://www.indeed.com/viewjob?jk=d1141cb25af0572d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Athena, Redshift, CI/CD, Git, Redshift, Kafka, Hadoop</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d347250384414c</t>
+          <t>https://www.indeed.com/viewjob?jk=2858e6cdb0b814c9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Full Stack Developer / Architect (ON-SITE ONLY)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, NoSQL</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,977 +846,977 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10066f0332c5b380</t>
+          <t>https://www.indeed.com/viewjob?jk=6ac17f0a96aca7cc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Engineer, Back-End</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb18c698bf09905f</t>
+          <t>https://www.indeed.com/viewjob?jk=252b57185b6bf6eb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>eCommerce Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Gemini, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d74b5348b7fd931</t>
+          <t>https://www.indeed.com/viewjob?jk=1e35e6d3eeb789a8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, Synapse, Snowflake, Redshift, Tableau, Power BI, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139ae06dd742f9ff</t>
+          <t>https://www.indeed.com/viewjob?jk=c84a9ad80a25316a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, Kubernetes, Git, Databricks, Python, R, Java</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd476055d1792da</t>
+          <t>https://www.indeed.com/viewjob?jk=4e0bbba83e98cb7d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, Kubernetes, Git, Databricks, Python, R, Java</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31499f71cdecb8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=6a9bc566048f5df7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, Kubernetes, Git, Databricks, Python, R, Java</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929da1d9b8d02da7</t>
+          <t>https://www.indeed.com/viewjob?jk=07dbb3c32bde48dd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, Kubernetes, Git, Databricks, Python, R, Java</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990f003e318fc7ee</t>
+          <t>https://www.indeed.com/viewjob?jk=d708df951507ab47</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, Kubernetes, Git, Databricks, Python, R, Java</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799fa0365ab63c88</t>
+          <t>https://www.indeed.com/viewjob?jk=a138a47066e21f31</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Git, Databricks, MongoDB, NoSQL, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e65e864080e6f228</t>
+          <t>https://www.indeed.com/viewjob?jk=828e340224aeed4c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Git, Databricks, MongoDB, NoSQL, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379a672460ecff73</t>
+          <t>https://www.indeed.com/viewjob?jk=9d5c114d610320b6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Scientist - National Federal Tax Services</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, CI/CD, Git, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c837980bd637052e</t>
+          <t>https://www.indeed.com/viewjob?jk=d9eaae039d447f44</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Infrastructure</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Voleon Group</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Athena, BigQuery, Docker, Kubernetes, Snowflake, BigQuery, Python, R, Java</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db0d7f2f67ae2037</t>
+          <t>https://www.indeed.com/viewjob?jk=ef3c6ca789d44c7a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Infrastructure</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Voleon Group</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Athena, BigQuery, Docker, Kubernetes, Snowflake, BigQuery, Python, R, Java</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc5c1209d3bf9f82</t>
+          <t>https://www.indeed.com/viewjob?jk=19e18b192bba610a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Infrastructure</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Voleon Group</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Athena, BigQuery, Docker, Kubernetes, Snowflake, BigQuery, Python, R, Java</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=288370e41eee0f1c</t>
+          <t>https://www.indeed.com/viewjob?jk=d2115cb3f12e4c99</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Insights &amp; Analytics Senior Data Engineer (Contract)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AlixPartners</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Data Lake, CI/CD, Snowflake, Databricks, PySpark, Power BI, SQL, R</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3a4117d82354a9</t>
+          <t>https://www.indeed.com/viewjob?jk=920ef31316c24dd8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ProCare solutions</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, MongoDB, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59621637da2df488</t>
+          <t>https://www.indeed.com/viewjob?jk=0d046720d327986f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3d31f0c32f7c708</t>
+          <t>https://www.indeed.com/viewjob?jk=69fa64d3d461b5cf</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=839dff8154a525fe</t>
+          <t>https://www.indeed.com/viewjob?jk=4a17a6382ee88f9b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer in Test – Performance Testing (Remote - US)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nextech Systems</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ece1679bb1b68d39</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8c40518a5768b2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Python, R, Optimization</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4c144c9967d41f3</t>
+          <t>https://www.indeed.com/viewjob?jk=a84bb0a592bfc72e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior AI Data Analytics Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BillGO, Inc.</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Git, Snowflake, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35205d14927a9d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=f3491babc6f5565a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer I</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Gen Digital Inc.</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, BigQuery, Git, BigQuery, Python, SQL, R, A/B Testing</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8378c32413f340a</t>
+          <t>https://www.indeed.com/viewjob?jk=8cdc4bde0029067a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, NoSQL, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=146fecf9cd2b1c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=ec57dc626511024d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Security Research Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Exabeam</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Git, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2887f3d4d109e5</t>
+          <t>https://www.indeed.com/viewjob?jk=7263d7409264ffdb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer I</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Baylor College of Medicine</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AI Engineer, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, R, Scala</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8822e9a8bbb9ce82</t>
+          <t>https://www.indeed.com/viewjob?jk=176e596d2f444780</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Associate Software Engineer – Full Stack (AI First)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, CI/CD, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16b99e4398857e63</t>
+          <t>https://www.indeed.com/viewjob?jk=f85b7deaaee8007c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Juneau, AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc96cc8b1713d38</t>
+          <t>https://www.indeed.com/viewjob?jk=ba7c08cc6925a2b0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Observability</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>Red Hat</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, Jenkins, Git, MySQL, MongoDB, Cassandra, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aab1e166ca443aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e93e4cf30b4bd0a5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Observability</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>LoadUp Technologies</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3820ff49875cde5</t>
+          <t>https://www.indeed.com/viewjob?jk=eace328fa21b6010</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. 3D C++ Software Engineer (On-site)</t>
+          <t>Software Engineer III - J2EE/Spring Boot</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Envista Holdings</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pomona, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Python, R, C++, Scala, Optimization</t>
+          <t>RAG, S3, Kubernetes, Git, Kafka, Cassandra, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,392 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089b12b1ad077cc1</t>
+          <t>https://www.indeed.com/viewjob?jk=ea46fe6dc4046714</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sr Platform Software Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Thistle Services LLC</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Kinesis, FastAPI, CI/CD, Terraform, Git, Kafka, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c68b52907b51544</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Snapsheet</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Docker, CI/CD, Terraform, Git, PostgreSQL, MySQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cfc7d98187fa164</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Unsecured Installments</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Upstart</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Git, Python, R, Java, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f4b3078f40d422a</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sr. Security Engineer, Infrastructure &amp; Platform Security</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11cd361dcfe299bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>QA Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Corpay</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Beaverton, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, EC2, CI/CD, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f4e776d60f6dbd9</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Software Engineer 2</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Hopkins, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bee7f3b1d3558f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Software Engineer 2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5331edf6c905499e</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Software Engineer 2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Earth City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd3b8341850dde41</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Junior Frontend Developer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, S3, CI/CD, Git, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47dfa774e632a9e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Unsecured Installments</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Upstart</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Burlingame, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Git, Python, R, Java, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59781903289c5260</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Global Partners LP</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Waltham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d677323b8f1a2636</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-09.xlsx
+++ b/daily_matches/job_matches_2026-07-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Scientist</t>
+          <t>Data Scientist I or II (MAD-BS-OR)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, CI/CD, Git, Snowflake, Databricks, Python, SQL</t>
+          <t>Data Scientist, RAG, FAISS, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c7b414f064a9a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=abbbc0e4fc791dd8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Senior Product Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lincolnshire, IL, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, Hadoop, Python, R, Scala</t>
+          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, Jenkins, Terraform, Git, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb06c9b2ec3eadbb</t>
+          <t>https://www.indeed.com/viewjob?jk=fc5c72de81426773</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist - Specialty Operations</t>
+          <t>Python AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Python, SQL, R, Optimization, Hypothesis Testing</t>
+          <t>AI Engineer, RAG, TensorFlow, FastAPI, Docker, CI/CD, Jenkins, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35bdfed6d04c7aa8</t>
+          <t>https://www.indeed.com/viewjob?jk=6e793e39138e9c31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Wellington, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, Keras, Git, PySpark, Python, SQL, R</t>
+          <t>RAG, Gemini, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70ffe5aa2d34caa2</t>
+          <t>https://www.indeed.com/viewjob?jk=dda7312d5b30e548</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist - Specialty Operations</t>
+          <t>Advanced Industrial Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Python, SQL, R, Optimization, Hypothesis Testing</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Azure ML, Docker, Kubernetes, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a595861ee87187b3</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c25c1aa79d8de6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Python Full Stack Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Jupiter IT Solutions LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, Keras, Git, PySpark, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52803e9dce4be204</t>
+          <t>https://www.indeed.com/viewjob?jk=8b16b6d540be9e0f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Full Stack Engineer (AI, Automation &amp; CRM Integrations)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Automation Agency</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, Keras, Git, PySpark, Python, SQL, R</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, Docker, CI/CD, Git, PostgreSQL, MongoDB, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b883cf8b5b32a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=fc469384b12092f5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Data Scientist, AI Foundations</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, Keras, Git, PySpark, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, PyTorch, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a766ff7ca3bcaaee</t>
+          <t>https://www.indeed.com/viewjob?jk=23c1ed5dc3b38c69</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer – MHTECHIN (USA)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>mhtechin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, Keras, Git, PySpark, Python, SQL, R</t>
+          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2866edd440ceb73</t>
+          <t>https://www.indeed.com/viewjob?jk=b83f09563e0a3d38</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>LLM Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, Keras, Git, PySpark, Python, SQL, R</t>
+          <t>RAG, AWS SageMaker, S3, EC2, Kinesis, CI/CD, Kafka, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf022d7c02c0a78</t>
+          <t>https://www.indeed.com/viewjob?jk=ff04139732f0a032</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Customer Success Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Carto</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, Keras, Git, PySpark, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f14e90aa982f0c6</t>
+          <t>https://www.indeed.com/viewjob?jk=5c832212e51e3d6b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer - Java and Spring WebFlux</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, Keras, Git, PySpark, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=193d48feb5bc85b0</t>
+          <t>https://www.indeed.com/viewjob?jk=94facea91683e65c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Visualization Professional</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, Keras, Git, PySpark, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, Redshift, Git, Snowflake, Redshift, Power BI, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b5821acdadeb0e2</t>
+          <t>https://www.indeed.com/viewjob?jk=c535f0577c23c870</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Sr AI/ML Engineer - Remote Nationwide or Hybrid in MN/DC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, Keras, Git, PySpark, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, Hugging Face, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b99f0d6c86a88d5</t>
+          <t>https://www.indeed.com/viewjob?jk=c0db1921a6e2c7fc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Python Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, Keras, Git, PySpark, Python, SQL, R</t>
+          <t>RAG, BigQuery, Data Lake, Dataflow, Terraform, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,77 +986,847 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=725a047f128d8a61</t>
+          <t>https://www.indeed.com/viewjob?jk=3a6b715c5b39bb01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Associate, Data Scientist - People Strategy &amp; Analytics</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, Keras, Git, PySpark, Python, SQL, R</t>
+          <t>Data Scientist, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee44e0d7d69ea571</t>
+          <t>https://www.indeed.com/viewjob?jk=e559cbb415f2f56e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Software Engineer - Java Microservices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Jenkins, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3997327881ddf00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Machine Learning Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Whatnot</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, AWS SageMaker, S3, EC2, Kinesis, Kafka, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11df9d24276f3911</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Prompt Engineering, Git, MySQL, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9906c5636975f423</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Solutions Engineer | East Coast - Remote</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85e80291b9c4fb91</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Cloud DevOps 4</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Sioux Falls, SD, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3661b7d8210b81e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Software Engineer 3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Sioux Falls, SD, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6c42591aa81b41d</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Scientist - US Card (Applied GenAI)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, LLaMA, Hugging Face, PyTorch, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fee8d143b9581e83</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Junior Frontend Developer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, S3, CI/CD, Git, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5396127204dfd5db</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Architect</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>OnIT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>10</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, XGBoost, Keras, Git, PySpark, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a51c97084df2869a</t>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a94e3ce102cb6fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Applied Scientist - Remote</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Generative AI, Prompt Engineering, Azure ML, Git, Snowflake, Databricks, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=862e00c065b9512b</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior GCP Cloud Platform Engineer - Landing Zone / Terraform</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DATA PULSE TECH AI LLC</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Gemini, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, BigQuery, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc7351fee2f2ca20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AI Analyst Intern</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MJMC, Inc.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Homewood, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eca0383f4503e439</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b263d37ffb84b8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Cloud Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sonar</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1137912cd4930b5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Jenkins, Terraform, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db4bf595e241e7c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer (AI Foundations)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6dfb4d7fb934d384</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer (AI Foundations)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b31a8ee3f8a1ea5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Scientist - Model Risk Office</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, PyTorch, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c4cc9550ec73cf0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sr.Dot Net Developer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Git, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9891af19d23ce0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sr.Dot Net Developer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Git, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9daf8f4dcafe4837</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior .Net Developer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Git, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=25b2ee2f76f5ddf8</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Technical Product Owner</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9fb9a4f3efc90c9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>React Web Developer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, S3, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d35ec12fbb079df</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-09.xlsx
+++ b/daily_matches/job_matches_2026-07-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,130 +468,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist I or II (MAD-BS-OR)</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>Master Electronics</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, FAISS, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, AKS</t>
+          <t>Data Scientist, PyTorch, S3, Redshift, MLflow, Docker, Kubernetes, CI/CD, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abbbc0e4fc791dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c73446a5f5a2ca0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer</t>
+          <t>AI/ML Solutions Architect - PostgreSQL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Docker, Kubernetes, Jenkins, Terraform, Git, MongoDB</t>
+          <t>Machine Learning Engineer, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, XGBoost, LightGBM, Apache Airflow, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc5c72de81426773</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d883bc65769a81</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Python AI Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, FastAPI, Docker, CI/CD, Jenkins, Git, Kafka, PostgreSQL</t>
+          <t>LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e793e39138e9c31</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe4d9a822bce57</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer</t>
+          <t>AI Engineer Sr</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wellington, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Gemini, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dda7312d5b30e548</t>
+          <t>https://www.indeed.com/viewjob?jk=078df3477d2cb69e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Advanced Industrial Software Engineer</t>
+          <t>AI Full Stack Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>BTI Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Washington, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Azure ML, Docker, Kubernetes, Databricks, Python, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c25c1aa79d8de6</t>
+          <t>https://www.indeed.com/viewjob?jk=d9d4d37bcb800e31</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Python Full Stack Developer</t>
+          <t>Java Application Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jupiter IT Solutions LLC</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Township of Jackson, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks, Kafka, Python, SQL</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b16b6d540be9e0f</t>
+          <t>https://www.indeed.com/viewjob?jk=26394a63af389d62</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (AI, Automation &amp; CRM Integrations)</t>
+          <t>Java Application Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Automation Agency</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, Docker, CI/CD, Git, PostgreSQL, MongoDB, SQL</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc469384b12092f5</t>
+          <t>https://www.indeed.com/viewjob?jk=2ba1ec9e7778b066</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, AI Foundations</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, PyTorch, Git, Python, SQL</t>
+          <t>Data Scientist, RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23c1ed5dc3b38c69</t>
+          <t>https://www.indeed.com/viewjob?jk=3044d3acb77883ad</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer – MHTECHIN (USA)</t>
+          <t>LLM Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>mhtechin</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL</t>
+          <t>RAG, AWS SageMaker, S3, EC2, Kinesis, CI/CD, Kafka, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83f09563e0a3d38</t>
+          <t>https://www.indeed.com/viewjob?jk=ae92ae66832c6772</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff04139732f0a032</t>
+          <t>https://www.indeed.com/viewjob?jk=458b51e37fb91a99</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Customer Success Engineer</t>
+          <t>LLM Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Carto</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Python, SQL</t>
+          <t>RAG, AWS SageMaker, S3, EC2, Kinesis, CI/CD, Kafka, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c832212e51e3d6b</t>
+          <t>https://www.indeed.com/viewjob?jk=26363a8e2499a65a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer - Java and Spring WebFlux</t>
+          <t>Jr. AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>sdna global</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94facea91683e65c</t>
+          <t>https://www.indeed.com/viewjob?jk=08c549ad8fb13296</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Visualization Professional</t>
+          <t>Cloud, AI &amp; DevOps Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Redshift, Git, Snowflake, Redshift, Power BI, SQL, R</t>
+          <t>RAG, Copilot, Synapse, FastAPI, CI/CD, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c535f0577c23c870</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c2d0d2b6c03086</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr AI/ML Engineer - Remote Nationwide or Hybrid in MN/DC</t>
+          <t>Sr. IT Cloud Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Reyes Holdings</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Hugging Face, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0db1921a6e2c7fc</t>
+          <t>https://www.indeed.com/viewjob?jk=cdfe2996ac74509c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Python Data Engineer</t>
+          <t>Research Programmer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, Dataflow, Terraform, BigQuery, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Docker, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a6b715c5b39bb01</t>
+          <t>https://www.indeed.com/viewjob?jk=025dcef4b127034e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - People Strategy &amp; Analytics</t>
+          <t>Fullstack Engineer, Marketing</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NCSA College Recruiting</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Snowflake, Python, SQL</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e559cbb415f2f56e</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9f56162e38c2b1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java Microservices</t>
+          <t>Fullstack Engineer, Marketing</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NCSA College Recruiting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Jenkins, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3997327881ddf00</t>
+          <t>https://www.indeed.com/viewjob?jk=c291169defa77d17</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Machine Learning Platform Engineer</t>
+          <t>Fullstack Engineer, Marketing</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>IMG Academy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, AWS SageMaker, S3, EC2, Kinesis, Kafka, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11df9d24276f3911</t>
+          <t>https://www.indeed.com/viewjob?jk=362edf60a4890cb4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Fullstack Engineer, Marketing</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>IMG Academy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Git, MySQL, NoSQL, Python, SQL, R, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9906c5636975f423</t>
+          <t>https://www.indeed.com/viewjob?jk=442d3e11f0a53f4c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Solutions Engineer | East Coast - Remote</t>
+          <t>Senior Scientific Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>n8n</t>
+          <t>Deep Origin</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Java, Julia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e80291b9c4fb91</t>
+          <t>https://www.indeed.com/viewjob?jk=9e8119093b65cdf3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud DevOps 4</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Alarm.com</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3661b7d8210b81e4</t>
+          <t>https://www.indeed.com/viewjob?jk=434eb0a34d9023b9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Senior AI/ML Engineer - Hybrid in Eden Prairie, MN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, PostgreSQL, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Azure ML, CI/CD, Git, Databricks, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c42591aa81b41d</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7297cab0b251e0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - US Card (Applied GenAI)</t>
+          <t>Software Development Engineer in Test - SDET</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NATIONMIND LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, Hugging Face, PyTorch, Python, SQL, R, Scala</t>
+          <t>Generative AI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fee8d143b9581e83</t>
+          <t>https://www.indeed.com/viewjob?jk=85066d85b25815ea</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Junior Frontend Developer</t>
+          <t>Machine Learning Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, S3, CI/CD, Git, R, Java, Optimization</t>
+          <t>RAG, AWS SageMaker, S3, EC2, Kinesis, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5396127204dfd5db</t>
+          <t>https://www.indeed.com/viewjob?jk=44755c8629392e7b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Machine Learning Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>OnIT</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>RAG, AWS SageMaker, S3, EC2, Kinesis, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a94e3ce102cb6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=955ca3ea8fb3bbba</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior AI/ML Applied Scientist - Remote</t>
+          <t>Machine Learning Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Generative AI, Prompt Engineering, Azure ML, Git, Snowflake, Databricks, Python, R, Optimization</t>
+          <t>RAG, AWS SageMaker, S3, EC2, Kinesis, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862e00c065b9512b</t>
+          <t>https://www.indeed.com/viewjob?jk=64e9006c80eb6865</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior GCP Cloud Platform Engineer - Landing Zone / Terraform</t>
+          <t>Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DATA PULSE TECH AI LLC</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gemini, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Git, BigQuery, R</t>
+          <t>RAG, AWS SageMaker, S3, EC2, Kinesis, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7351fee2f2ca20</t>
+          <t>https://www.indeed.com/viewjob?jk=0d8d754a2c1f2400</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Analyst Intern</t>
+          <t>Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MJMC, Inc.</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Homewood, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>RAG, AWS SageMaker, S3, EC2, Kinesis, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca0383f4503e439</t>
+          <t>https://www.indeed.com/viewjob?jk=f9cc452d9eb90058</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+          <t>RAG, AWS SageMaker, S3, EC2, Kinesis, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b263d37ffb84b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=42260d914acad6bb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sonar</t>
+          <t>Whatnot</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, AWS SageMaker, S3, EC2, Kinesis, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,129 +1511,129 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1137912cd4930b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=f552ce2d666fdee5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Consultant, IT Infrastructure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Docker, Jenkins, Terraform, Git, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4bf595e241e7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=f959bf645970c329</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (AI Foundations)</t>
+          <t>Senior Consultant, IT Infrastructure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dfb4d7fb934d384</t>
+          <t>https://www.indeed.com/viewjob?jk=e02f6278ccc70ba8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (AI Foundations)</t>
+          <t>AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
+          <t>AI Engineer, RAG, PyTorch, MLflow, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31a8ee3f8a1ea5b</t>
+          <t>https://www.indeed.com/viewjob?jk=e15982bf2d2e66a3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - Model Risk Office</t>
+          <t>Data and Automation Engineer - Python</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Plum Inc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, PyTorch, Python, R, Scala</t>
+          <t>RAG, Copilot, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c4cc9550ec73cf0</t>
+          <t>https://www.indeed.com/viewjob?jk=a3724ae53a7e9f39</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr.Dot Net Developer</t>
+          <t>Data and Automation Engineer - Python</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Plum Inc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9891af19d23ce0a</t>
+          <t>https://www.indeed.com/viewjob?jk=12de8ce2bbd02d4b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr.Dot Net Developer</t>
+          <t>Data and Automation Engineer - Python</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Plum Inc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9daf8f4dcafe4837</t>
+          <t>https://www.indeed.com/viewjob?jk=df6f29475e80e513</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior .Net Developer</t>
+          <t>Data and Automation Engineer - Python</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Plum Inc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,77 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b2ee2f76f5ddf8</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Technical Product Owner</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb9a4f3efc90c9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>React Web Developer</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, S3, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4d35ec12fbb079df</t>
+          <t>https://www.indeed.com/viewjob?jk=38038606552c4596</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-09.xlsx
+++ b/daily_matches/job_matches_2026-07-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,130 +468,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Master Electronics</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, PyTorch, S3, Redshift, MLflow, Docker, Kubernetes, CI/CD, Databricks, Redshift</t>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c73446a5f5a2ca0</t>
+          <t>https://www.indeed.com/viewjob?jk=4952bffe58e2575f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Solutions Architect - PostgreSQL</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, XGBoost, LightGBM, Apache Airflow, CI/CD</t>
+          <t>LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d883bc65769a81</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b642838eb4a6bb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Penetration Tester</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, Docker, Kubernetes, CI/CD, Git</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Power BI, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe4d9a822bce57</t>
+          <t>https://www.indeed.com/viewjob?jk=8b2d7835a40e0de0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer Sr</t>
+          <t>Java/Python Engineer - Santa Clara, CA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Calypso Way</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, CI/CD</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=078df3477d2cb69e</t>
+          <t>https://www.indeed.com/viewjob?jk=160dcf0991158470</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Full Stack Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BTI Solutions</t>
+          <t>ＡＮＧＥＬ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, NoSQL</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9d4d37bcb800e31</t>
+          <t>https://www.indeed.com/viewjob?jk=85fb541fb41505df</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Java Application Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>IGT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Township of Jackson, NJ, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
+          <t>Generative AI, RAG, S3, Apache Airflow, CI/CD, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26394a63af389d62</t>
+          <t>https://www.indeed.com/viewjob?jk=ccfeb0ae91c8b22c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java Application Developer</t>
+          <t>Full Stack Engineer (AI, Automation &amp; CRM Integrations) - USA Applicants Only</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Automation Agency</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL</t>
+          <t>LangChain, RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ba1ec9e7778b066</t>
+          <t>https://www.indeed.com/viewjob?jk=eb6b11c837e2f9ad</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Customer Success Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Carto</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, Python</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3044d3acb77883ad</t>
+          <t>https://www.indeed.com/viewjob?jk=decc557b90cc77e0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LLM Platform Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, AWS SageMaker, S3, EC2, Kinesis, CI/CD, Kafka, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Data Lake, Git, Snowflake, Databricks, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae92ae66832c6772</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8ebe939dba44ab</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LLM Platform Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, AWS SageMaker, S3, EC2, Kinesis, CI/CD, Kafka, PostgreSQL, Python, SQL</t>
+          <t>AI Engineer, RAG, CI/CD, Git, Snowflake, Kafka, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=458b51e37fb91a99</t>
+          <t>https://www.indeed.com/viewjob?jk=f39cc18ceb9ab518</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LLM Platform Engineer</t>
+          <t>MBSE &amp; Digital Threads Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Whatnot</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, AWS SageMaker, S3, EC2, Kinesis, CI/CD, Kafka, PostgreSQL, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, CI/CD, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26363a8e2499a65a</t>
+          <t>https://www.indeed.com/viewjob?jk=95de75c7a56461d5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jr. AI Engineer</t>
+          <t>Software Engineer, Infrastructure &amp; Reliability</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sdna global</t>
+          <t>crewAI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java</t>
+          <t>FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c549ad8fb13296</t>
+          <t>https://www.indeed.com/viewjob?jk=815d89b6892addc0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud, AI &amp; DevOps Engineer II</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>Merkle, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Synapse, FastAPI, CI/CD, Git, Databricks, Python, SQL, R</t>
+          <t>Generative AI, RAG, BigQuery, Data Lake, Snowflake, Databricks, BigQuery, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c2d0d2b6c03086</t>
+          <t>https://www.indeed.com/viewjob?jk=602b8a7eb823221f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. IT Cloud Engineer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Reyes Holdings</t>
+          <t>New York Power Authority</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, RAG, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdfe2996ac74509c</t>
+          <t>https://www.indeed.com/viewjob?jk=51bc8587c9569f9c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Research Programmer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Two Six Technologies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, LangChain, RAG, Docker, Kubernetes, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025dcef4b127034e</t>
+          <t>https://www.indeed.com/viewjob?jk=ae6dee9a2ebe94cf</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Fullstack Engineer, Marketing</t>
+          <t>Software Quality Assurance Engineer III (Contractor) ID - 806914</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NCSA College Recruiting</t>
+          <t>RE/SPEC Inc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9f56162e38c2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=4de1cfb61be7d587</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Fullstack Engineer, Marketing</t>
+          <t>Software Quality Assurance Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NCSA College Recruiting</t>
+          <t>Skywalk Global</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c291169defa77d17</t>
+          <t>https://www.indeed.com/viewjob?jk=68539dfb183fa557</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fullstack Engineer, Marketing</t>
+          <t>Software Engineer (Python)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IMG Academy</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, MySQL, SQL, R, Java</t>
+          <t>Generative AI, S3, EC2, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362edf60a4890cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=285d6d84144f7525</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Fullstack Engineer, Marketing</t>
+          <t>Quality Assurance Analyst</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IMG Academy</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=442d3e11f0a53f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c670a5a1c3c8ce</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Scientific Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deep Origin</t>
+          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Java, Julia</t>
+          <t>Copilot, CI/CD, NoSQL, Power BI, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e8119093b65cdf3</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2ad1fb8f369d3c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GenAI Engineer - VectorDBand PostgreSQL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Alarm.com</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, Pinecone, Prompt Engineering, FastAPI, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,567 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=434eb0a34d9023b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior AI/ML Engineer - Hybrid in Eden Prairie, MN</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Azure ML, CI/CD, Git, Databricks, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a7297cab0b251e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test - SDET</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>NATIONMIND LLC</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85066d85b25815ea</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Machine Learning Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Whatnot</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, AWS SageMaker, S3, EC2, Kinesis, Kafka, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44755c8629392e7b</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Machine Learning Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Whatnot</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, AWS SageMaker, S3, EC2, Kinesis, Kafka, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=955ca3ea8fb3bbba</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Machine Learning Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Whatnot</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, AWS SageMaker, S3, EC2, Kinesis, Kafka, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64e9006c80eb6865</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Machine Learning Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Whatnot</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, AWS SageMaker, S3, EC2, Kinesis, Kafka, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d8d754a2c1f2400</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Machine Learning Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Whatnot</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, AWS SageMaker, S3, EC2, Kinesis, Kafka, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f9cc452d9eb90058</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Machine Learning Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Whatnot</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, AWS SageMaker, S3, EC2, Kinesis, Kafka, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=42260d914acad6bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Machine Learning Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Whatnot</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, AWS SageMaker, S3, EC2, Kinesis, Kafka, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f552ce2d666fdee5</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Senior Consultant, IT Infrastructure</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Dell Technologies</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Round Rock, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f959bf645970c329</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior Consultant, IT Infrastructure</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Dell Technologies</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e02f6278ccc70ba8</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>AI/ML Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, PyTorch, MLflow, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e15982bf2d2e66a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Data and Automation Engineer - Python</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Plum Inc</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a3724ae53a7e9f39</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Data and Automation Engineer - Python</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Plum Inc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=12de8ce2bbd02d4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Data and Automation Engineer - Python</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Plum Inc</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df6f29475e80e513</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Data and Automation Engineer - Python</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Plum Inc</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=38038606552c4596</t>
+          <t>https://www.indeed.com/viewjob?jk=4108d5f3e2c32e79</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-09.xlsx
+++ b/daily_matches/job_matches_2026-07-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Jenkins</t>
+          <t>LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4952bffe58e2575f</t>
+          <t>https://www.indeed.com/viewjob?jk=8b802a7acff1d5ad</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Data Analytics AI Consultant</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, Docker, Kubernetes, CI/CD, Git</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Data Lake, MLflow, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b642838eb4a6bb</t>
+          <t>https://www.indeed.com/viewjob?jk=a1b4be9cc729ff54</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Penetration Tester</t>
+          <t>Entry-Level Engineer – Python, Data Analytics &amp; Generative AI Life Sciences Commercial</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Power BI, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2d7835a40e0de0</t>
+          <t>https://www.indeed.com/viewjob?jk=fecc4311cdc7d492</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Java/Python Engineer - Santa Clara, CA</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Calypso Way</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python</t>
+          <t>LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=160dcf0991158470</t>
+          <t>https://www.indeed.com/viewjob?jk=33562b3072fa72c3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Snowflake Architect - DBT and Cortex AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ＡＮＧＥＬ</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Mettawa, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+          <t>RAG, Cortex, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark, Kafka, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fb541fb41505df</t>
+          <t>https://www.indeed.com/viewjob?jk=aed7e6578e3c4d9c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IGT</t>
+          <t>OFFICE HOURS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Apache Airflow, CI/CD, Git, Databricks, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccfeb0ae91c8b22c</t>
+          <t>https://www.indeed.com/viewjob?jk=af024982951791dc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (AI, Automation &amp; CRM Integrations) - USA Applicants Only</t>
+          <t>Senior Site Reliability Engineer (REMOTE)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Automation Agency</t>
+          <t>Discogs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, MongoDB, SQL, R</t>
+          <t>S3, FastAPI, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, MySQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb6b11c837e2f9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a924459fc3278a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Customer Success Engineer</t>
+          <t>Agentic AI Data Engineer - CMC Data Integration</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Carto</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Python, SQL</t>
+          <t>Data Scientist, LLaMA, S3, Glue, Redshift, CI/CD, GitHub Actions, Git, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decc557b90cc77e0</t>
+          <t>https://www.indeed.com/viewjob?jk=39a6a17108976060</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior AI Ops Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Data Lake, Git, Snowflake, Databricks, Tableau, Python, SQL</t>
+          <t>Data Scientist, RAG, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8ebe939dba44ab</t>
+          <t>https://www.indeed.com/viewjob?jk=0397954acef41867</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Machine Learning Engineer, Bidding Science</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Unity Technologies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, CI/CD, Git, Snowflake, Kafka, Hadoop, Python, SQL, R</t>
+          <t>Machine Learning Engineer, RAG, Copilot, PyTorch, BigQuery, Git, BigQuery, Python, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f39cc18ceb9ab518</t>
+          <t>https://www.indeed.com/viewjob?jk=4120868c0edb5ded</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MBSE &amp; Digital Threads Engineer</t>
+          <t>Senior Machine Learning Engineer, Bidding Science</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Unity Technologies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, CI/CD, GitHub Actions, Git, Python, R</t>
+          <t>Machine Learning Engineer, RAG, Copilot, PyTorch, BigQuery, Git, BigQuery, Python, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95de75c7a56461d5</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a2c660c5047203</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure &amp; Reliability</t>
+          <t>Finance Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>crewAI</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,11 +867,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL</t>
+          <t>RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau, Power BI, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815d89b6892addc0</t>
+          <t>https://www.indeed.com/viewjob?jk=bc59d1bea902c70f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Merkle, Inc.</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, Data Lake, Snowflake, Databricks, BigQuery, R, Scala, Optimization</t>
+          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=602b8a7eb823221f</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce6e57ea03bfddf</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>AI Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>New York Power Authority</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, Copilot, FastAPI, Docker, Kubernetes, CI/CD, Python, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51bc8587c9569f9c</t>
+          <t>https://www.indeed.com/viewjob?jk=2eff46f4e868210f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - Java/React/Kafka/Scala</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Two Six Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Docker, Kubernetes, NoSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Redshift, Kubernetes, CI/CD, Git, Redshift, Kafka, Python, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae6dee9a2ebe94cf</t>
+          <t>https://www.indeed.com/viewjob?jk=4d2a2d9ec51c42aa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Quality Assurance Engineer III (Contractor) ID - 806914</t>
+          <t>Data Scientist, Modeler</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RE/SPEC Inc</t>
+          <t>Teleflora</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Gemini, Prompt Engineering, BigQuery, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de1cfb61be7d587</t>
+          <t>https://www.indeed.com/viewjob?jk=b3bd3244b8329cca</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Quality Assurance Analyst</t>
+          <t>Senior Analytics Engineer (Finance)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Skywalk Global</t>
+          <t>Whoop</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
+          <t>RAG, Prompt Engineering, Cortex, CI/CD, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68539dfb183fa557</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf327b1921f6141</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer (Python)</t>
+          <t>Machine Learning / AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>HomeKYND</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, S3, EC2, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, Generative AI, Hugging Face, TensorFlow, PyTorch, Keras, YOLO, AWS SageMaker, Python, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=285d6d84144f7525</t>
+          <t>https://www.indeed.com/viewjob?jk=d2477075835573b9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst</t>
+          <t>Data Governance Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Tenaska, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
+          <t>RAG, Data Lake, Git, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c670a5a1c3c8ce</t>
+          <t>https://www.indeed.com/viewjob?jk=9526e415d7243069</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NATIONAL ASSOCIATION OF REALTORS®</t>
+          <t>Parachute Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Copilot, CI/CD, NoSQL, Power BI, SQL, R, Java, Scala, Optimization</t>
+          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,42 +1161,462 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2ad1fb8f369d3c</t>
+          <t>https://www.indeed.com/viewjob?jk=b50f7e51b39938d2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GenAI Engineer - VectorDBand PostgreSQL</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b6dcae3ab81891c</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MBSE &amp; Digital Threads Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>El Segundo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba516e35b78699cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Enterprise Architect</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dentsu</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Central, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, BigQuery, Data Lake, Snowflake, Databricks, BigQuery, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4783b2b567ca329</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Enterprise Architect</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dentsu</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Central, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, BigQuery, Data Lake, Snowflake, Databricks, BigQuery, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c59ed7c5cb948815</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Platform Engineer III</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Hudson Manpower</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Kafka, Hadoop, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d37ddb64259e2b2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Software Quality Assurance Analyst</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Intellibee Inc</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ID, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>10</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, Pinecone, Prompt Engineering, FastAPI, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4108d5f3e2c32e79</t>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3f029833970b78d</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer (Java &amp; AI-Driven Development)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NiCE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0990564a7dc36af</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Engineer (Java &amp; AI-Driven Development)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NiCE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Jenkins, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=990d3c2cee60bdfb</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI Architect</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, BigQuery, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afc9b4104cfcebaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI Architect</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Gemini, BigQuery, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7eafb102886a6929</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, LLaMA, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5822a50b92418cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Sr AI Strategist - Trading &amp; Data Platforms</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NextEra Energy</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Juno Beach, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1838dc35896e0d2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Associate - AI-driven Lab Automation for Life Sciences</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Brookhaven National Laboratory</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Upton, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55032c056ddfbc13</t>
         </is>
       </c>
     </row>
